--- a/artfynd/A 29724-2022 artfynd.xlsx
+++ b/artfynd/A 29724-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29724-2022 artfynd.xlsx
+++ b/artfynd/A 29724-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103045565</v>
       </c>
       <c r="B2" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447648.8227501212</v>
+        <v>447649</v>
       </c>
       <c r="R2" t="n">
-        <v>6478398.596963072</v>
+        <v>6478399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -815,12 +800,7 @@
         <v>103767828</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447667.9895335711</v>
+        <v>447668</v>
       </c>
       <c r="R3" t="n">
-        <v>6478302.01453508</v>
+        <v>6478301</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,19 +877,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,12 +910,7 @@
         <v>106283936</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447688.7548641735</v>
+        <v>447689</v>
       </c>
       <c r="R4" t="n">
-        <v>6478325.296127947</v>
+        <v>6478325</v>
       </c>
       <c r="S4" t="n">
         <v>63</v>
@@ -1022,19 +987,9 @@
           <t>2023-01-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1020,7 @@
         <v>106284019</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447628.6744704446</v>
+        <v>447628</v>
       </c>
       <c r="R5" t="n">
-        <v>6478264.321646851</v>
+        <v>6478264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,19 +1097,9 @@
           <t>2023-01-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-01-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,12 +1130,7 @@
         <v>108022735</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447500.8896220342</v>
+        <v>447501</v>
       </c>
       <c r="R6" t="n">
-        <v>6478317.857609035</v>
+        <v>6478317</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,19 +1203,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108022755</v>
+        <v>108022751</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1263,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1356,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447780.286659405</v>
+        <v>447577</v>
       </c>
       <c r="R7" t="n">
-        <v>6478306.277601731</v>
+        <v>6478311</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1389,19 +1309,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,15 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108022751</v>
+        <v>108022755</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1369,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1477,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447577.3670988739</v>
+        <v>447780</v>
       </c>
       <c r="R8" t="n">
-        <v>6478310.553162273</v>
+        <v>6478306</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1510,19 +1415,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
